--- a/product_upload/packages/52/file.xlsx
+++ b/product_upload/packages/52/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -669,7 +674,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -831,6 +836,11 @@
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
+        <is>
+          <t>Vyvanse</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
         <is>
           <t>SKU-49DC6D2A7731</t>
         </is>
@@ -851,7 +861,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1017,6 +1027,11 @@
         </is>
       </c>
       <c r="AT3" t="inlineStr">
+        <is>
+          <t>Vyvanse</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
         <is>
           <t>SKU-4F3688897E83</t>
         </is>
@@ -1037,7 +1052,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1199,6 +1214,11 @@
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
+        <is>
+          <t>Vyvanse</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
         <is>
           <t>SKU-6486095E8A6A</t>
         </is>
@@ -1219,7 +1239,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1377,6 +1397,11 @@
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
+        <is>
+          <t>Vyvanse</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
         <is>
           <t>SKU-C00E475C0C2B</t>
         </is>
@@ -1397,7 +1422,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1563,6 +1588,11 @@
         </is>
       </c>
       <c r="AT6" t="inlineStr">
+        <is>
+          <t>Vyvanse</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
         <is>
           <t>SKU-23BB2C2600DF</t>
         </is>
@@ -1583,7 +1613,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1745,6 +1775,11 @@
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
+        <is>
+          <t>Vyvanse</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
         <is>
           <t>SKU-2FE065FF4945</t>
         </is>
@@ -1765,7 +1800,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1921,6 +1956,11 @@
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
+        <is>
+          <t>PROVINDA</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
         <is>
           <t>SKU-8BAF69A5CCDE</t>
         </is>
@@ -1941,7 +1981,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2107,6 +2147,11 @@
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
+        <is>
+          <t>PROVINDA</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
         <is>
           <t>SKU-89B8E3DEF4E1</t>
         </is>
@@ -2127,7 +2172,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2287,6 +2332,11 @@
         </is>
       </c>
       <c r="AT10" t="inlineStr">
+        <is>
+          <t>Valgaset</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
         <is>
           <t>SKU-8E2A520352DD</t>
         </is>
@@ -2307,7 +2357,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2467,6 +2517,11 @@
         </is>
       </c>
       <c r="AT11" t="inlineStr">
+        <is>
+          <t>Pifeltro</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
         <is>
           <t>SKU-11775012F02C</t>
         </is>
@@ -2487,7 +2542,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2647,6 +2702,11 @@
         </is>
       </c>
       <c r="AT12" t="inlineStr">
+        <is>
+          <t>Xofax</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
         <is>
           <t>SKU-D102C6770A84</t>
         </is>
@@ -2667,7 +2727,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2827,6 +2887,11 @@
         </is>
       </c>
       <c r="AT13" t="inlineStr">
+        <is>
+          <t>Xofax</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
         <is>
           <t>SKU-7FA0A3CD5B6B</t>
         </is>
@@ -2847,7 +2912,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3007,6 +3072,11 @@
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
+        <is>
+          <t>Xofax</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
         <is>
           <t>SKU-D6722CAE27DD</t>
         </is>
@@ -3027,7 +3097,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3197,6 +3267,11 @@
         </is>
       </c>
       <c r="AT15" t="inlineStr">
+        <is>
+          <t>Licarb</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
         <is>
           <t>SKU-EBF706934C25</t>
         </is>
@@ -3217,7 +3292,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3391,6 +3466,11 @@
         </is>
       </c>
       <c r="AT16" t="inlineStr">
+        <is>
+          <t>Tadil</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
         <is>
           <t>SKU-AA2A52118C30</t>
         </is>
@@ -3411,7 +3491,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3577,6 +3657,11 @@
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
+        <is>
+          <t>Tadil</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
         <is>
           <t>SKU-D67F73ED37A9</t>
         </is>
@@ -3597,7 +3682,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3763,6 +3848,11 @@
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
+        <is>
+          <t>LIBSA</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
         <is>
           <t>SKU-2572373D1B6E</t>
         </is>
@@ -3783,7 +3873,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3949,6 +4039,11 @@
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
+        <is>
+          <t>Libsa</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
         <is>
           <t>SKU-FDEC3A4348DD</t>
         </is>
@@ -3969,7 +4064,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4139,6 +4234,11 @@
         </is>
       </c>
       <c r="AT20" t="inlineStr">
+        <is>
+          <t>Libsa</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
         <is>
           <t>SKU-D012B718855F</t>
         </is>
@@ -4159,7 +4259,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4329,6 +4429,11 @@
         </is>
       </c>
       <c r="AT21" t="inlineStr">
+        <is>
+          <t>Libsa</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
         <is>
           <t>SKU-44B22F5237CA</t>
         </is>
@@ -4349,7 +4454,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4507,6 +4612,11 @@
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
+        <is>
+          <t>Uxorate</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
         <is>
           <t>SKU-4363CD272143</t>
         </is>
@@ -4527,7 +4637,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4699,6 +4809,11 @@
         </is>
       </c>
       <c r="AT23" t="inlineStr">
+        <is>
+          <t>ABILIRAZOLE</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
         <is>
           <t>SKU-6A9295C869D6</t>
         </is>
@@ -4719,7 +4834,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4873,6 +4988,11 @@
       <c r="AR24" t="inlineStr"/>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
+        <is>
+          <t>Domassel</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
         <is>
           <t>SKU-A175E488E024</t>
         </is>
@@ -4893,7 +5013,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5064,6 +5184,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>Mounjaro</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-7D7410C7CF0E</t>
         </is>
       </c>
@@ -5083,7 +5208,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5254,6 +5379,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>Mounjaro</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-4F94877629A0</t>
         </is>
       </c>
@@ -5273,7 +5403,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5444,6 +5574,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>Mounjaro</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-2A8E10BF7352</t>
         </is>
       </c>
@@ -5463,7 +5598,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5634,6 +5769,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>Mounjaro</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-6140802A4E9A</t>
         </is>
       </c>
@@ -5653,7 +5793,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5828,6 +5968,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>Mounjaro</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-1EC2D9A57F7E</t>
         </is>
       </c>
@@ -5847,7 +5992,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6019,6 +6164,11 @@
         </is>
       </c>
       <c r="AT30" t="inlineStr">
+        <is>
+          <t>Rinvoq</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
         <is>
           <t>SKU-E2C454996770</t>
         </is>
@@ -6039,7 +6189,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6213,6 +6363,11 @@
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
+        <is>
+          <t>LIPOCOMB</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
         <is>
           <t>SKU-534089BC82AB</t>
         </is>
@@ -6233,7 +6388,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6407,6 +6562,11 @@
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
+        <is>
+          <t>LIPOCOMB</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
         <is>
           <t>SKU-6368675289E5</t>
         </is>
@@ -6427,7 +6587,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6585,6 +6745,11 @@
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
+        <is>
+          <t>Vigolev</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
         <is>
           <t>SKU-52049369267E</t>
         </is>
@@ -6605,7 +6770,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6767,6 +6932,11 @@
         </is>
       </c>
       <c r="AT34" t="inlineStr">
+        <is>
+          <t>Vigolev</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
         <is>
           <t>SKU-F2C3AE68E08B</t>
         </is>
@@ -6787,7 +6957,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6947,6 +7117,11 @@
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
+        <is>
+          <t>Ornivoda</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
         <is>
           <t>SKU-7450B24A5485</t>
         </is>
@@ -6967,7 +7142,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7142,6 +7317,11 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>Mounjaro</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-22955814C97F</t>
         </is>
       </c>
@@ -7161,7 +7341,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7317,6 +7497,11 @@
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
+        <is>
+          <t>Oneclapz</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
         <is>
           <t>SKU-7B1D888A632E</t>
         </is>
@@ -7337,7 +7522,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7495,6 +7680,11 @@
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
+        <is>
+          <t>Eralyce</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
         <is>
           <t>SKU-20769406C432</t>
         </is>
@@ -7515,7 +7705,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7677,6 +7867,11 @@
         </is>
       </c>
       <c r="AT39" t="inlineStr">
+        <is>
+          <t>Etorigen</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
         <is>
           <t>SKU-E64ABEAF47B3</t>
         </is>
@@ -7697,7 +7892,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7853,6 +8048,11 @@
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
+        <is>
+          <t>Etorigen</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
         <is>
           <t>SKU-58C83CD7EF96</t>
         </is>
@@ -7873,7 +8073,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8025,6 +8225,11 @@
       <c r="AR41" t="inlineStr"/>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
+        <is>
+          <t>Etorigen</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
         <is>
           <t>SKU-DE44F17E1A5C</t>
         </is>
@@ -8045,7 +8250,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8211,6 +8416,11 @@
         </is>
       </c>
       <c r="AT42" t="inlineStr">
+        <is>
+          <t>NORMOSANG</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
         <is>
           <t>SKU-3BFD79E9890F</t>
         </is>
@@ -8231,7 +8441,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8393,6 +8603,11 @@
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
+        <is>
+          <t>Tadil</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
         <is>
           <t>SKU-754EC442184C</t>
         </is>
@@ -8413,7 +8628,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8579,6 +8794,11 @@
         </is>
       </c>
       <c r="AT44" t="inlineStr">
+        <is>
+          <t>Tadil</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
         <is>
           <t>SKU-ABFCC55CDBA9</t>
         </is>
@@ -8599,7 +8819,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8759,6 +8979,11 @@
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
+        <is>
+          <t>Etoruma</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
         <is>
           <t>SKU-A48C016939F3</t>
         </is>
@@ -8779,7 +9004,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8943,6 +9168,11 @@
         </is>
       </c>
       <c r="AT46" t="inlineStr">
+        <is>
+          <t>Etoruma</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
         <is>
           <t>SKU-969B3CCEFBF0</t>
         </is>
@@ -8963,7 +9193,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9119,6 +9349,11 @@
       <c r="AR47" t="inlineStr"/>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
+        <is>
+          <t>Etoruma</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
         <is>
           <t>SKU-C3E2D58FC1E1</t>
         </is>
@@ -9139,7 +9374,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9303,6 +9538,11 @@
         </is>
       </c>
       <c r="AT48" t="inlineStr">
+        <is>
+          <t>Sertidep</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
         <is>
           <t>SKU-C2B58B9DDC6F</t>
         </is>
@@ -9323,7 +9563,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9481,6 +9721,11 @@
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
+        <is>
+          <t>MONTELAIR ORAL GRANULES</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
         <is>
           <t>SKU-4D21FE648CA4</t>
         </is>
@@ -9501,7 +9746,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9661,6 +9906,11 @@
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
+        <is>
+          <t>Xolamol</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
         <is>
           <t>SKU-781AA4A67379</t>
         </is>
@@ -9681,7 +9931,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9833,6 +10083,11 @@
       <c r="AR51" t="inlineStr"/>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
+        <is>
+          <t>Bivocard</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
         <is>
           <t>SKU-C9B5084D13D5</t>
         </is>
@@ -9853,7 +10108,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10015,6 +10270,11 @@
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
+        <is>
+          <t>Xaluprine</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
         <is>
           <t>SKU-19D82B2FB55E</t>
         </is>
@@ -10035,7 +10295,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10197,6 +10457,11 @@
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
+        <is>
+          <t>Zympass</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
         <is>
           <t>SKU-1800E9FB6F38</t>
         </is>
@@ -10217,7 +10482,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10383,6 +10648,11 @@
         </is>
       </c>
       <c r="AT54" t="inlineStr">
+        <is>
+          <t>Zympass</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
         <is>
           <t>SKU-8B25BB7A9429</t>
         </is>
@@ -10403,7 +10673,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10567,6 +10837,11 @@
         </is>
       </c>
       <c r="AT55" t="inlineStr">
+        <is>
+          <t>Zympass</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
         <is>
           <t>SKU-99D870CDCB91</t>
         </is>
@@ -10587,7 +10862,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10749,6 +11024,11 @@
         </is>
       </c>
       <c r="AT56" t="inlineStr">
+        <is>
+          <t>Muxava</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
         <is>
           <t>SKU-98B182630CB8</t>
         </is>
@@ -10769,7 +11049,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10927,6 +11207,11 @@
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
+        <is>
+          <t>Muxava</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
         <is>
           <t>SKU-B65EC7C344F2</t>
         </is>
@@ -10947,7 +11232,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11117,6 +11402,11 @@
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
+        <is>
+          <t>Cefodox</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
         <is>
           <t>SKU-2796E2D24583</t>
         </is>
@@ -11137,7 +11427,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11297,6 +11587,11 @@
         </is>
       </c>
       <c r="AT59" t="inlineStr">
+        <is>
+          <t>Celenax</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
         <is>
           <t>SKU-285C6267CBB2</t>
         </is>
@@ -11317,7 +11612,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11473,6 +11768,11 @@
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
+        <is>
+          <t>Bistonal</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
         <is>
           <t>SKU-86D5454CF31D</t>
         </is>
@@ -11493,7 +11793,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11653,6 +11953,11 @@
         </is>
       </c>
       <c r="AT61" t="inlineStr">
+        <is>
+          <t>Bistonal</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
         <is>
           <t>SKU-B6314F5F416F</t>
         </is>
@@ -11673,7 +11978,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11833,6 +12138,11 @@
         </is>
       </c>
       <c r="AT62" t="inlineStr">
+        <is>
+          <t>Bistonal</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
         <is>
           <t>SKU-C41BDA2B91FC</t>
         </is>
@@ -11853,7 +12163,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12019,6 +12329,11 @@
         </is>
       </c>
       <c r="AT63" t="inlineStr">
+        <is>
+          <t>Evrenzo</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
         <is>
           <t>SKU-1483D7E8C3FF</t>
         </is>
@@ -12039,7 +12354,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12205,6 +12520,11 @@
         </is>
       </c>
       <c r="AT64" t="inlineStr">
+        <is>
+          <t>Evrenzo</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
         <is>
           <t>SKU-4DC6043282ED</t>
         </is>
@@ -12225,7 +12545,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12391,6 +12711,11 @@
         </is>
       </c>
       <c r="AT65" t="inlineStr">
+        <is>
+          <t>Evrenzo</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
         <is>
           <t>SKU-F673A91E8E5A</t>
         </is>
@@ -12411,7 +12736,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12567,6 +12892,11 @@
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
+        <is>
+          <t>Aminglu</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
         <is>
           <t>SKU-22E3B66515FC</t>
         </is>
@@ -12587,7 +12917,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12747,6 +13077,11 @@
         </is>
       </c>
       <c r="AT67" t="inlineStr">
+        <is>
+          <t>Eletrivaz</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
         <is>
           <t>SKU-E04A6A8831E8</t>
         </is>
@@ -12767,7 +13102,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12937,6 +13272,11 @@
         </is>
       </c>
       <c r="AT68" t="inlineStr">
+        <is>
+          <t>DABITRAN</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
         <is>
           <t>SKU-1B2B14981C38</t>
         </is>
@@ -12957,7 +13297,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13119,6 +13459,11 @@
       <c r="AR69" t="inlineStr"/>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
+        <is>
+          <t>DABITRAN</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
         <is>
           <t>SKU-2A7FC8DD8E3E</t>
         </is>
@@ -13139,7 +13484,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13305,6 +13650,11 @@
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
+        <is>
+          <t>Ojox</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
         <is>
           <t>SKU-53C89BAFD0B7</t>
         </is>
@@ -13325,7 +13675,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13499,6 +13849,11 @@
         </is>
       </c>
       <c r="AT71" t="inlineStr">
+        <is>
+          <t>Devasc</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
         <is>
           <t>SKU-A723057EB74E</t>
         </is>
@@ -13519,7 +13874,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13673,6 +14028,11 @@
       <c r="AR72" t="inlineStr"/>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
+        <is>
+          <t>LUNIA</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
         <is>
           <t>SKU-B265BFBFCF6B</t>
         </is>
@@ -13693,7 +14053,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -13847,6 +14207,11 @@
       <c r="AR73" t="inlineStr"/>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
+        <is>
+          <t>LUNIA</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
         <is>
           <t>SKU-7B2FB6D86B88</t>
         </is>
@@ -13867,7 +14232,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14023,6 +14388,11 @@
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
+        <is>
+          <t>Moxiwar</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
         <is>
           <t>SKU-69E2158EFD06</t>
         </is>
@@ -14043,7 +14413,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14203,6 +14573,11 @@
       <c r="AR75" t="inlineStr"/>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
+        <is>
+          <t>Seroflo 50/100 Ciphaler</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
         <is>
           <t>SKU-4B5E125FE30E</t>
         </is>
@@ -14223,7 +14598,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14395,6 +14770,11 @@
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
+        <is>
+          <t>Seroflo 50/250 Ciphaler</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
         <is>
           <t>SKU-CA0B24B8576E</t>
         </is>
@@ -14415,7 +14795,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14577,6 +14957,11 @@
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
+        <is>
+          <t>Fylibix</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
         <is>
           <t>SKU-156AA42CFD99</t>
         </is>
@@ -14597,7 +14982,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -14759,6 +15144,11 @@
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
+        <is>
+          <t>Fylibix</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
         <is>
           <t>SKU-3CAB2E22AE69</t>
         </is>
@@ -14779,7 +15169,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -14947,6 +15337,11 @@
         </is>
       </c>
       <c r="AT79" t="inlineStr">
+        <is>
+          <t>Lanacet</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
         <is>
           <t>SKU-5CE9C39C0652</t>
         </is>
@@ -14967,7 +15362,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15135,6 +15530,11 @@
         </is>
       </c>
       <c r="AT80" t="inlineStr">
+        <is>
+          <t>Lanacet</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
         <is>
           <t>SKU-ACD2CF626A58</t>
         </is>
@@ -15155,7 +15555,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15319,6 +15719,11 @@
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
+        <is>
+          <t>Lanacet</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
         <is>
           <t>SKU-8322D6D08BB6</t>
         </is>
@@ -15339,7 +15744,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15503,6 +15908,11 @@
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
+        <is>
+          <t>Loradeel</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
         <is>
           <t>SKU-F5FEA6CD042E</t>
         </is>
@@ -15523,7 +15933,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15679,6 +16089,11 @@
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
+        <is>
+          <t>Rosgan</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
         <is>
           <t>SKU-C1764640745B</t>
         </is>
@@ -15699,7 +16114,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -15863,6 +16278,11 @@
         </is>
       </c>
       <c r="AT84" t="inlineStr">
+        <is>
+          <t>Lotac</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
         <is>
           <t>SKU-4197056B6850</t>
         </is>
@@ -15883,7 +16303,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16037,6 +16457,11 @@
       <c r="AR85" t="inlineStr"/>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
+        <is>
+          <t>Lotac</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
         <is>
           <t>SKU-30C11807FBB8</t>
         </is>
@@ -16057,7 +16482,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16233,6 +16658,11 @@
         </is>
       </c>
       <c r="AT86" t="inlineStr">
+        <is>
+          <t>Seroflo 50/500 ciphaler</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
         <is>
           <t>SKU-87D2879AF5CE</t>
         </is>
@@ -16253,7 +16683,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16411,6 +16841,11 @@
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
+        <is>
+          <t>Extaq</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
         <is>
           <t>SKU-53C8C05C3B48</t>
         </is>
@@ -16431,7 +16866,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16589,6 +17024,11 @@
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
+        <is>
+          <t>Extaq</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
         <is>
           <t>SKU-04D332E2F677</t>
         </is>
@@ -16609,7 +17049,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16771,6 +17211,11 @@
         </is>
       </c>
       <c r="AT89" t="inlineStr">
+        <is>
+          <t>Extaq</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
         <is>
           <t>SKU-57D7C4256350</t>
         </is>
@@ -16791,7 +17236,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16949,6 +17394,11 @@
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
+        <is>
+          <t>Extaq</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
         <is>
           <t>SKU-6D5EC864A273</t>
         </is>
@@ -16969,7 +17419,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17137,6 +17587,11 @@
         </is>
       </c>
       <c r="AT91" t="inlineStr">
+        <is>
+          <t>DROLINA</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
         <is>
           <t>SKU-2D0EE6CF80E9</t>
         </is>
@@ -17157,7 +17612,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17331,6 +17786,11 @@
         </is>
       </c>
       <c r="AT92" t="inlineStr">
+        <is>
+          <t>Apdx</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
         <is>
           <t>SKU-9945B93C5A1C</t>
         </is>
@@ -17351,7 +17811,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17521,6 +17981,11 @@
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
+        <is>
+          <t>Apdx</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
         <is>
           <t>SKU-2488C0172A47</t>
         </is>
@@ -17541,7 +18006,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -17711,6 +18176,11 @@
         </is>
       </c>
       <c r="AT94" t="inlineStr">
+        <is>
+          <t>Vostifaz</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
         <is>
           <t>SKU-CCE75B9E9329</t>
         </is>
@@ -17731,7 +18201,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -17905,6 +18375,11 @@
         </is>
       </c>
       <c r="AT95" t="inlineStr">
+        <is>
+          <t>Vetam</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
         <is>
           <t>SKU-1E22703056E1</t>
         </is>
@@ -17925,7 +18400,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18099,6 +18574,11 @@
         </is>
       </c>
       <c r="AT96" t="inlineStr">
+        <is>
+          <t>Vetam</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
         <is>
           <t>SKU-714FFDC3E4C9</t>
         </is>
@@ -18119,7 +18599,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18277,6 +18757,11 @@
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
+        <is>
+          <t>Omezyn Plus</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
         <is>
           <t>SKU-BAB8BFFA99CC</t>
         </is>
@@ -18297,7 +18782,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18455,6 +18940,11 @@
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
+        <is>
+          <t>REZMYG</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
         <is>
           <t>SKU-4F23C9B611B4</t>
         </is>
@@ -18475,7 +18965,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18637,6 +19127,11 @@
         </is>
       </c>
       <c r="AT99" t="inlineStr">
+        <is>
+          <t>REZMYG</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
         <is>
           <t>SKU-81E82B90857C</t>
         </is>
@@ -18657,7 +19152,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -18815,6 +19310,11 @@
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
+        <is>
+          <t>Panda Advance</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
         <is>
           <t>SKU-0FB10701130A</t>
         </is>
@@ -18835,7 +19335,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19007,6 +19507,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>Prasido</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-DC2B2AEC6255</t>
         </is>
@@ -19023,7 +19528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19069,100 +19574,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19194,7 +19704,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19209,92 +19719,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-56378</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>494.31</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>508</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19326,7 +19841,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19341,92 +19856,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-42273</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>322.41</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>509</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19458,7 +19978,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19473,92 +19993,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-16554</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>305.49</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>510</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19590,7 +20115,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19605,92 +20130,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-84306</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>89.03</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>511</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19722,7 +20252,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -19737,92 +20267,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-97683</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>118</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>512</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19854,7 +20389,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -19869,92 +20404,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-18472</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>309.58</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>513</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19986,7 +20526,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20001,92 +20541,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-91795</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>51.1</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>514</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20118,7 +20663,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20133,92 +20678,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-58598</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>485.8</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>515</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20250,7 +20800,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20265,92 +20815,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-46075</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>271.54</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>516</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20382,7 +20937,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20397,92 +20952,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-84981</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>117.68</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>517</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20514,7 +21074,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20529,92 +21089,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-56429</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>127.38</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>518</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20631,7 +21196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20737,6 +21302,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -20772,7 +21347,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -20837,6 +21412,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-4C50383A968A</t>
         </is>
@@ -20873,7 +21458,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -20938,6 +21523,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-19A464D79464</t>
         </is>
@@ -20974,7 +21569,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21039,6 +21634,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-AB0A0FEAF4BA</t>
         </is>
@@ -21075,7 +21680,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21140,6 +21745,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-CDBC728B712B</t>
         </is>
@@ -21176,7 +21791,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21241,6 +21856,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-DC47F52DB3B2</t>
         </is>
@@ -21277,7 +21902,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21342,6 +21967,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-5B820C510370</t>
         </is>
@@ -21378,7 +22013,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21443,6 +22078,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-E8995A7C1C55</t>
         </is>
@@ -21479,7 +22124,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21544,6 +22189,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-22F20E2327E9</t>
         </is>
@@ -21580,7 +22235,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21645,6 +22300,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-E054D419A206</t>
         </is>
@@ -21681,7 +22346,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -21746,6 +22411,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-0385D8D5E5D9</t>
         </is>
@@ -21782,7 +22457,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -21847,6 +22522,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-736BD3F56B71</t>
         </is>
@@ -21883,7 +22568,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -21948,6 +22633,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-8AA33DAE04FA</t>
         </is>
@@ -21984,7 +22679,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22049,6 +22744,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-9DA0AEAE120B</t>
         </is>
@@ -22085,7 +22790,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22150,6 +22855,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-470BF0045D12</t>
         </is>
@@ -22186,7 +22901,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22251,6 +22966,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-E9FB3FA2DE9F</t>
         </is>
@@ -22287,7 +23012,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22352,6 +23077,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-3DCDFD2B08D0</t>
         </is>
@@ -22388,7 +23123,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22453,6 +23188,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-8B6899DE36AD</t>
         </is>
@@ -22489,7 +23234,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22554,6 +23299,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-A450DF584ED3</t>
         </is>
@@ -22590,7 +23345,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -22655,6 +23410,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-72BA24416A51</t>
         </is>
@@ -22691,7 +23456,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -22756,6 +23521,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-3E097C77A2C6</t>
         </is>

--- a/product_upload/packages/52/file.xlsx
+++ b/product_upload/packages/52/file.xlsx
@@ -682,8 +682,16 @@
           <t>2456506407-269-536949466074</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vyvanse</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vyvanse detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -869,8 +877,16 @@
           <t>4826831407-305-456683565152</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vyvanse</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vyvanse detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1060,8 +1076,16 @@
           <t>8949719458-076-649550691363</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vyvanse</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vyvanse detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1247,8 +1271,16 @@
           <t>2111710917-584-003246547854</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vyvanse</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vyvanse detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1430,8 +1462,16 @@
           <t>9952035483-069-806416161121</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vyvanse</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vyvanse detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1621,8 +1661,16 @@
           <t>9543299241-448-475022248577</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vyvanse</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vyvanse detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1808,8 +1856,16 @@
           <t>1415443405-720-172917158376</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PROVINDA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>PROVINDA detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2180,8 +2236,16 @@
           <t>1707317871-365-675532800029</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Valgaset</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Valgaset detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2365,8 +2429,16 @@
           <t>9668247919-393-853346255688</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pifeltro</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Pifeltro detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2550,8 +2622,16 @@
           <t>4685141234-632-022326809332</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Xofax</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Xofax detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2735,8 +2815,16 @@
           <t>2954292473-460-611973758949</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Xofax</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Xofax detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -4462,8 +4550,16 @@
           <t>7376807382-995-809971134586</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Uxorate</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Uxorate detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4842,8 +4938,16 @@
           <t>4516535220-759-181755639165</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Domassel</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Domassel detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>Pharma Pharmaceutical Industries (PPI)</t>
@@ -6595,8 +6699,16 @@
           <t>9786804601-742-458828317345</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vigolev</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Vigolev detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6778,8 +6890,16 @@
           <t>9405780846-553-671512429087</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vigolev</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Vigolev detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -6965,8 +7085,16 @@
           <t>7509599313-553-332926863779</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ornivoda</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Ornivoda detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7349,8 +7477,16 @@
           <t>8715046499-870-457159891560</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Oneclapz</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Oneclapz detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7530,8 +7666,16 @@
           <t>2842221161-567-111796155434</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Eralyce</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Eralyce detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7713,8 +7857,16 @@
           <t>2643473340-869-761512129102</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Etorigen</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Etorigen detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -7900,8 +8052,16 @@
           <t>6497801394-249-758628533956</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Etorigen</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Etorigen detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -8081,8 +8241,16 @@
           <t>6980822023-561-172773015067</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Etorigen</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Etorigen detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8258,8 +8426,16 @@
           <t>5785077349-976-681346062439</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NORMOSANG</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>NORMOSANG detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8449,8 +8625,16 @@
           <t>5977232059-492-609396314391</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tadil</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Tadil detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8636,8 +8820,16 @@
           <t>4338606412-090-072591275725</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tadil</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Tadil detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -8827,8 +9019,16 @@
           <t>7315234240-929-353006637953</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Etoruma</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Etoruma detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">Razy Al Madina Pharmaceutical	</t>
@@ -9012,8 +9212,16 @@
           <t>3210236552-213-929434873911</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Etoruma</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Etoruma detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">Razy Al Madina Pharmaceutical	</t>
@@ -9201,8 +9409,16 @@
           <t>6854588394-910-066405698427</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Etoruma</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Etoruma detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">Razy Al Madina Pharmaceutical	</t>
@@ -9382,8 +9598,16 @@
           <t>1973001659-692-680453237156</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sertidep</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sertidep detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -9571,8 +9795,16 @@
           <t>8730683312-036-401369642652</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MONTELAIR ORAL GRANULES</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>MONTELAIR ORAL GRANULES detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -9754,8 +9986,16 @@
           <t>0751409954-515-348215461892</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Xolamol</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Xolamol detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -9939,8 +10179,16 @@
           <t>0383297496-518-431396083387</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Bivocard</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Bivocard detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10116,8 +10364,16 @@
           <t>0613060477-969-302793805687</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Xaluprine</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Xaluprine detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10303,8 +10559,16 @@
           <t>6855159796-454-955956085618</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zympass</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Zympass detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10490,8 +10754,16 @@
           <t>1562142001-002-723489883314</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zympass</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Zympass detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10681,8 +10953,16 @@
           <t>4113425789-548-690045344708</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zympass</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Zympass detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -10870,8 +11150,16 @@
           <t>8111197921-488-499068061903</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Muxava</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Muxava detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -11057,8 +11345,16 @@
           <t>2642002500-371-118375769516</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Muxava</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Muxava detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11435,8 +11731,16 @@
           <t>5337023766-461-137785589327</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Celenax</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Celenax detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11620,8 +11924,16 @@
           <t>2459474870-455-219707562524</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Bistonal</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Bistonal detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -11801,8 +12113,16 @@
           <t>4554168949-438-738729213285</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Bistonal</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bistonal detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -11986,8 +12306,16 @@
           <t>0785218894-694-883866849249</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Bistonal</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bistonal detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12171,8 +12499,16 @@
           <t>2648582775-260-282495432927</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Evrenzo</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Evrenzo detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12362,8 +12698,16 @@
           <t>8022680279-824-528661621505</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Evrenzo</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Evrenzo detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12553,8 +12897,16 @@
           <t>9570374236-588-326793214874</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Evrenzo</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Evrenzo detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -12744,8 +13096,16 @@
           <t>1933947465-406-469705636303</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Aminglu</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Aminglu detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -12925,8 +13285,16 @@
           <t>7250265475-522-025218304498</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Eletrivaz</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Eletrivaz detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13882,8 +14250,16 @@
           <t>9326310887-396-439575835331</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LUNIA</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>LUNIA detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -14061,8 +14437,16 @@
           <t>9281532417-605-447171905275</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LUNIA</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>LUNIA detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14240,8 +14624,16 @@
           <t>6214170957-495-536311871190</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Moxiwar</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Moxiwar detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14421,8 +14813,16 @@
           <t>1399078527-168-486724683178</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Seroflo 50/100 Ciphaler</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Seroflo 50/100 Ciphaler detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
           <t>Sudair Pharma Company</t>
@@ -14803,8 +15203,16 @@
           <t>8303248522-019-573894331279</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Fylibix</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Fylibix detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -14990,8 +15398,16 @@
           <t>9649755917-622-873390682915</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Fylibix</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Fylibix detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -15177,8 +15593,16 @@
           <t>6751222717-619-933861527067</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lanacet</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Lanacet detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
           <t>Dallah Pharma Factory</t>
@@ -15370,8 +15794,16 @@
           <t>1603792312-645-911015086751</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lanacet</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Lanacet detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
           <t>Dallah Pharma Factory</t>
@@ -15563,8 +15995,16 @@
           <t>9655668323-800-211109215689</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lanacet</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Lanacet detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
           <t>Dallah Pharma Factory</t>
@@ -15941,8 +16381,16 @@
           <t>8795275626-598-614751515295</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rosgan</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Rosgan detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16122,8 +16570,16 @@
           <t>9246771732-479-986509894970</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lotac</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Lotac detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
           <t>Alrai Pharmaceutical industry Co. (L.L.C)</t>
@@ -16311,8 +16767,16 @@
           <t>3590773738-322-096487608984</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lotac</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Lotac detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -16691,8 +17155,16 @@
           <t>1786778920-049-867754329689</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Extaq</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Extaq detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -16874,8 +17346,16 @@
           <t>7308182183-476-187335313126</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Extaq</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Extaq detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17057,8 +17537,16 @@
           <t>0065851661-601-563659156220</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Extaq</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Extaq detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17244,8 +17732,16 @@
           <t>9393485025-742-898989277544</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Extaq</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Extaq detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -18607,8 +19103,16 @@
           <t>7988576326-530-418869777787</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Omezyn Plus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Omezyn Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -18790,8 +19294,16 @@
           <t>6559414198-182-893741674587</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REZMYG</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>REZMYG detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -18973,8 +19485,16 @@
           <t>9325472513-417-053477385571</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REZMYG</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>REZMYG detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -19160,8 +19680,16 @@
           <t>5034384763-989-145394858373</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Panda Advance</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Panda Advance detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/52/file.xlsx
+++ b/product_upload/packages/52/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20102,7 +20102,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21805,40 +21805,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -21918,38 +21923,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>271.49</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-4C50383A968A</t>
         </is>
@@ -22029,38 +22039,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>238.46</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-19A464D79464</t>
         </is>
@@ -22140,38 +22155,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>67.77</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-AB0A0FEAF4BA</t>
         </is>
@@ -22251,38 +22271,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>149.75</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-CDBC728B712B</t>
         </is>
@@ -22362,38 +22387,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>166.84</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-DC47F52DB3B2</t>
         </is>
@@ -22473,38 +22503,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>261.49</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-5B820C510370</t>
         </is>
@@ -22584,38 +22619,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>32.85</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-E8995A7C1C55</t>
         </is>
@@ -22695,38 +22735,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>337.69</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-22F20E2327E9</t>
         </is>
@@ -22806,38 +22851,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>29.91</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-E054D419A206</t>
         </is>
@@ -22917,38 +22967,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>65.05</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-0385D8D5E5D9</t>
         </is>
@@ -23028,38 +23083,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>99.95</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-736BD3F56B71</t>
         </is>
@@ -23139,38 +23199,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>45.34</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-8AA33DAE04FA</t>
         </is>
@@ -23250,38 +23315,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>65.70999999999999</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-9DA0AEAE120B</t>
         </is>
@@ -23361,38 +23431,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>154.14</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-470BF0045D12</t>
         </is>
@@ -23472,38 +23547,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>452.7</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-E9FB3FA2DE9F</t>
         </is>
@@ -23583,38 +23663,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>220.16</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-3DCDFD2B08D0</t>
         </is>
@@ -23694,38 +23779,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>286.16</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-8B6899DE36AD</t>
         </is>
@@ -23805,38 +23895,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>63.47</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-A450DF584ED3</t>
         </is>
@@ -23916,38 +24011,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>451.54</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-72BA24416A51</t>
         </is>
@@ -24027,38 +24127,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>244.19</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-3E097C77A2C6</t>
         </is>
